--- a/templates/CLF_CoNgay.xlsx
+++ b/templates/CLF_CoNgay.xlsx
@@ -479,7 +479,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -516,6 +516,30 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -526,13 +550,37 @@
         <color indexed="64"/>
       </top>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -555,12 +603,18 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -606,6 +660,12 @@
     <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -630,10 +690,16 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -642,6 +708,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -692,6 +764,9 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1128,414 +1203,440 @@
     <col min="256" max="16385" style="5" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="77" customHeight="1" spans="5:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="E1" s="8"/>
-      <c r="F1" s="9" t="s">
+    <row r="1" ht="77" customHeight="1" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="8"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-    </row>
-    <row r="2" ht="27.5" customHeight="1" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="11"/>
-      <c r="B2" s="12" t="s">
+      <c r="G1" s="10"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+    </row>
+    <row r="2" ht="27.5" customHeight="1" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="13"/>
+      <c r="B2" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-    </row>
-    <row r="3" ht="67" customHeight="1" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="14"/>
-      <c r="B3" s="15"/>
-      <c r="C3" s="16" t="s">
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+    </row>
+    <row r="3" ht="67" customHeight="1" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="16"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="17"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="9" t="s">
+      <c r="D3" s="19"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="9"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-    </row>
-    <row r="4" ht="25" customHeight="1" spans="1:14" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="20"/>
-      <c r="B4" s="21" t="s">
+      <c r="G3" s="10"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="11"/>
+    </row>
+    <row r="4" ht="25" customHeight="1" spans="1:14" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="22"/>
+      <c r="B4" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="21" t="s">
+      <c r="D4" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="21" t="s">
+      <c r="E4" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="21" t="s">
+      <c r="F4" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="21" t="s">
+      <c r="G4" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="22" t="s">
+      <c r="H4" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="I4" s="22" t="s">
+      <c r="I4" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="J4" s="21" t="s">
+      <c r="J4" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="M4" s="23"/>
-      <c r="N4" s="23"/>
-    </row>
-    <row r="5" ht="25" customHeight="1" spans="1:14" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="20"/>
-      <c r="B5" s="24" t="s">
+      <c r="K4" s="21"/>
+      <c r="L4" s="21"/>
+      <c r="M4" s="25"/>
+      <c r="N4" s="25"/>
+    </row>
+    <row r="5" ht="25" customHeight="1" spans="1:14" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="22"/>
+      <c r="B5" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="24"/>
-      <c r="D5" s="24"/>
-      <c r="E5" s="24"/>
-      <c r="F5" s="24"/>
-      <c r="G5" s="24"/>
-      <c r="H5" s="24"/>
-      <c r="I5" s="24"/>
-      <c r="J5" s="24"/>
-      <c r="K5" s="25"/>
-      <c r="M5" s="23"/>
-      <c r="N5" s="23"/>
-    </row>
-    <row r="6" ht="42" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B6" s="26">
+      <c r="C5" s="27"/>
+      <c r="D5" s="27"/>
+      <c r="E5" s="27"/>
+      <c r="F5" s="27"/>
+      <c r="G5" s="27"/>
+      <c r="H5" s="27"/>
+      <c r="I5" s="27"/>
+      <c r="J5" s="28"/>
+      <c r="K5" s="29"/>
+      <c r="L5" s="21"/>
+      <c r="M5" s="25"/>
+      <c r="N5" s="25"/>
+    </row>
+    <row r="6" ht="42" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="1"/>
+      <c r="B6" s="30">
         <v>1</v>
       </c>
-      <c r="C6" s="27" t="s">
+      <c r="C6" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="28" t="s">
+      <c r="D6" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="29" t="s">
+      <c r="E6" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="34">
         <v>3</v>
       </c>
-      <c r="G6" s="30"/>
-      <c r="H6" s="31">
+      <c r="G6" s="34"/>
+      <c r="H6" s="35">
         <v>450000</v>
       </c>
-      <c r="I6" s="31">
+      <c r="I6" s="35">
         <f>H6*F6</f>
         <v>1350000</v>
       </c>
-      <c r="J6" s="32"/>
-    </row>
-    <row r="7" ht="45" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B7" s="33">
+      <c r="J6" s="36"/>
+    </row>
+    <row r="7" ht="45" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="1"/>
+      <c r="B7" s="37">
         <v>2</v>
       </c>
-      <c r="C7" s="34" t="s">
+      <c r="C7" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="28" t="s">
+      <c r="D7" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="E7" s="29" t="s">
+      <c r="E7" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="34">
         <f>15*5</f>
         <v>75</v>
       </c>
-      <c r="G7" s="30"/>
-      <c r="H7" s="31">
+      <c r="G7" s="34"/>
+      <c r="H7" s="35">
         <v>360000</v>
       </c>
-      <c r="I7" s="31">
+      <c r="I7" s="35">
         <f>H7*F7</f>
         <v>27000000</v>
       </c>
-      <c r="J7" s="32"/>
-    </row>
-    <row r="8" ht="39.5" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B8" s="33"/>
-      <c r="C8" s="34"/>
-      <c r="D8" s="35" t="s">
+      <c r="J7" s="36"/>
+    </row>
+    <row r="8" ht="39.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="1"/>
+      <c r="B8" s="39"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="29" t="s">
+      <c r="E8" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="34">
         <v>1</v>
       </c>
-      <c r="G8" s="30"/>
-      <c r="H8" s="31">
+      <c r="G8" s="34"/>
+      <c r="H8" s="35">
         <f>8*1.9*950000</f>
         <v>14440000</v>
       </c>
-      <c r="I8" s="31">
+      <c r="I8" s="35">
         <f>H8*F8</f>
         <v>14440000</v>
       </c>
-      <c r="J8" s="32"/>
-      <c r="K8" s="36"/>
-    </row>
-    <row r="9" ht="24" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B9" s="33"/>
-      <c r="C9" s="34"/>
-      <c r="D9" s="28" t="s">
+      <c r="J8" s="36"/>
+      <c r="K8" s="42"/>
+    </row>
+    <row r="9" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="1"/>
+      <c r="B9" s="43"/>
+      <c r="C9" s="44"/>
+      <c r="D9" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="E9" s="29" t="s">
+      <c r="E9" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="34">
         <v>14</v>
       </c>
-      <c r="G9" s="30"/>
-      <c r="H9" s="31">
+      <c r="G9" s="34"/>
+      <c r="H9" s="35">
         <v>300000</v>
       </c>
-      <c r="I9" s="31">
+      <c r="I9" s="35">
         <f>H9*F9</f>
         <v>4200000</v>
       </c>
-      <c r="J9" s="32"/>
-    </row>
-    <row r="10" ht="46" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B10" s="33">
+      <c r="J9" s="36"/>
+    </row>
+    <row r="10" ht="46" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="1"/>
+      <c r="B10" s="37">
         <v>3</v>
       </c>
-      <c r="C10" s="34" t="s">
+      <c r="C10" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="28" t="s">
+      <c r="D10" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="E10" s="29" t="s">
+      <c r="E10" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="F10" s="30">
+      <c r="F10" s="34">
         <f>9*5</f>
         <v>45</v>
       </c>
-      <c r="G10" s="30"/>
-      <c r="H10" s="31">
+      <c r="G10" s="34"/>
+      <c r="H10" s="35">
         <v>360000</v>
       </c>
-      <c r="I10" s="31">
+      <c r="I10" s="35">
         <f>H10*F10</f>
         <v>16200000</v>
       </c>
-      <c r="J10" s="32"/>
-    </row>
-    <row r="11" ht="46" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B11" s="33"/>
-      <c r="C11" s="34"/>
-      <c r="D11" s="28" t="s">
+      <c r="J10" s="36"/>
+    </row>
+    <row r="11" ht="46" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="1"/>
+      <c r="B11" s="39"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="E11" s="29" t="s">
+      <c r="E11" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="30">
+      <c r="F11" s="34">
         <v>1</v>
       </c>
-      <c r="G11" s="30"/>
-      <c r="H11" s="31">
+      <c r="G11" s="34"/>
+      <c r="H11" s="35">
         <f>5*2*290000+800000</f>
         <v>3700000</v>
       </c>
-      <c r="I11" s="31">
+      <c r="I11" s="35">
         <f>H11*F11</f>
         <v>3700000</v>
       </c>
-      <c r="J11" s="32"/>
-    </row>
-    <row r="12" ht="46" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B12" s="33"/>
-      <c r="C12" s="34"/>
-      <c r="D12" s="28" t="s">
+      <c r="J11" s="36"/>
+    </row>
+    <row r="12" ht="46" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="1"/>
+      <c r="B12" s="43"/>
+      <c r="C12" s="44"/>
+      <c r="D12" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="E12" s="29" t="s">
+      <c r="E12" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="F12" s="30">
+      <c r="F12" s="34">
         <v>1</v>
       </c>
-      <c r="G12" s="30"/>
-      <c r="H12" s="31">
+      <c r="G12" s="34"/>
+      <c r="H12" s="35">
         <f>9*2.5*360000</f>
         <v>8100000</v>
       </c>
-      <c r="I12" s="31">
+      <c r="I12" s="35">
         <f>H12*F12</f>
         <v>8100000</v>
       </c>
-      <c r="J12" s="32"/>
-    </row>
-    <row r="13" ht="21" customHeight="1" spans="1:13" s="37" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="38"/>
-      <c r="B13" s="39" t="s">
+      <c r="J12" s="36"/>
+    </row>
+    <row r="13" ht="21" customHeight="1" spans="1:13" s="45" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="46"/>
+      <c r="B13" s="47" t="s">
         <v>27</v>
       </c>
-      <c r="C13" s="39"/>
-      <c r="D13" s="39"/>
-      <c r="E13" s="39"/>
-      <c r="F13" s="39"/>
-      <c r="G13" s="39"/>
-      <c r="H13" s="39"/>
-      <c r="I13" s="40">
+      <c r="C13" s="47"/>
+      <c r="D13" s="47"/>
+      <c r="E13" s="47"/>
+      <c r="F13" s="47"/>
+      <c r="G13" s="47"/>
+      <c r="H13" s="47"/>
+      <c r="I13" s="48">
         <f>SUM(I6:I12)</f>
         <v>74990000</v>
       </c>
-      <c r="J13" s="41"/>
-      <c r="K13" s="42"/>
-      <c r="L13" s="42"/>
-      <c r="M13" s="43"/>
-    </row>
-    <row r="14" ht="21" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B14" s="39" t="s">
+      <c r="J13" s="49"/>
+      <c r="K13" s="50"/>
+      <c r="L13" s="50"/>
+      <c r="M13" s="51"/>
+    </row>
+    <row r="14" ht="21" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="39"/>
-      <c r="D14" s="39"/>
-      <c r="E14" s="39"/>
-      <c r="F14" s="39"/>
-      <c r="G14" s="39"/>
-      <c r="H14" s="39"/>
-      <c r="I14" s="44">
+      <c r="C14" s="47"/>
+      <c r="D14" s="47"/>
+      <c r="E14" s="47"/>
+      <c r="F14" s="47"/>
+      <c r="G14" s="47"/>
+      <c r="H14" s="47"/>
+      <c r="I14" s="52">
         <f>I13*8%</f>
         <v>5999200</v>
       </c>
-      <c r="J14" s="37"/>
-    </row>
-    <row r="15" ht="21" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B15" s="39" t="s">
+      <c r="J14" s="45"/>
+    </row>
+    <row r="15" ht="21" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="1"/>
+      <c r="B15" s="47" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="39"/>
-      <c r="D15" s="39"/>
-      <c r="E15" s="39"/>
-      <c r="F15" s="39"/>
-      <c r="G15" s="39"/>
-      <c r="H15" s="39"/>
-      <c r="I15" s="44">
+      <c r="C15" s="47"/>
+      <c r="D15" s="47"/>
+      <c r="E15" s="47"/>
+      <c r="F15" s="47"/>
+      <c r="G15" s="47"/>
+      <c r="H15" s="47"/>
+      <c r="I15" s="52">
         <f>I13+I14</f>
         <v>80989200</v>
       </c>
     </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="45"/>
-      <c r="C16" s="46"/>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="1"/>
+      <c r="B16" s="53"/>
+      <c r="C16" s="54"/>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
     </row>
-    <row r="17" ht="61" customHeight="1" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C17" s="47" t="s">
+    <row r="17" ht="61" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="1"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="55" t="s">
         <v>30</v>
       </c>
-      <c r="D17" s="47"/>
-      <c r="E17" s="48"/>
-      <c r="F17" s="49"/>
-      <c r="G17" s="49"/>
-      <c r="H17" s="50" t="s">
+      <c r="D17" s="55"/>
+      <c r="E17" s="56"/>
+      <c r="F17" s="57"/>
+      <c r="G17" s="57"/>
+      <c r="H17" s="58" t="s">
         <v>31</v>
       </c>
-      <c r="I17" s="51"/>
-    </row>
-    <row r="18" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C18" s="52" t="s">
+      <c r="I17" s="59"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="1"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="60" t="s">
         <v>32</v>
       </c>
-      <c r="D18" s="52"/>
-      <c r="E18" s="53"/>
-      <c r="F18" s="52"/>
-      <c r="G18" s="52"/>
-      <c r="H18" s="52" t="s">
+      <c r="D18" s="60"/>
+      <c r="E18" s="61"/>
+      <c r="F18" s="60"/>
+      <c r="G18" s="60"/>
+      <c r="H18" s="60" t="s">
         <v>33</v>
       </c>
-      <c r="I18" s="53"/>
+      <c r="I18" s="61"/>
     </row>
     <row r="19" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
-      <c r="C19" s="53"/>
-      <c r="D19" s="53"/>
-      <c r="E19" s="52"/>
-      <c r="F19" s="52"/>
-      <c r="G19" s="52"/>
-      <c r="H19" s="54"/>
-      <c r="I19" s="53"/>
+      <c r="B19" s="62"/>
+      <c r="C19" s="61"/>
+      <c r="D19" s="61"/>
+      <c r="E19" s="60"/>
+      <c r="F19" s="60"/>
+      <c r="G19" s="60"/>
+      <c r="H19" s="63"/>
+      <c r="I19" s="61"/>
+      <c r="J19" s="4"/>
       <c r="K19" s="5"/>
       <c r="L19" s="5"/>
       <c r="M19" s="6"/>
-      <c r="N19" s="55"/>
+      <c r="N19" s="64"/>
     </row>
     <row r="20" ht="24" customHeight="1" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5"/>
-      <c r="B20" s="45"/>
-      <c r="C20" s="53"/>
-      <c r="D20" s="53"/>
-      <c r="E20" s="52"/>
-      <c r="F20" s="52"/>
-      <c r="G20" s="52"/>
-      <c r="H20" s="54"/>
-      <c r="I20" s="53"/>
+      <c r="B20" s="53"/>
+      <c r="C20" s="61"/>
+      <c r="D20" s="61"/>
+      <c r="E20" s="60"/>
+      <c r="F20" s="60"/>
+      <c r="G20" s="60"/>
+      <c r="H20" s="63"/>
+      <c r="I20" s="61"/>
+      <c r="J20" s="4"/>
       <c r="K20" s="5"/>
       <c r="L20" s="5"/>
       <c r="M20" s="6"/>
-      <c r="N20" s="55"/>
+      <c r="N20" s="64"/>
     </row>
     <row r="21" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5"/>
-      <c r="B21" s="56"/>
-      <c r="C21" s="53"/>
-      <c r="D21" s="53"/>
-      <c r="E21" s="52"/>
-      <c r="F21" s="52"/>
-      <c r="G21" s="52"/>
-      <c r="H21" s="54"/>
-      <c r="I21" s="53"/>
+      <c r="B21" s="65"/>
+      <c r="C21" s="61"/>
+      <c r="D21" s="61"/>
+      <c r="E21" s="60"/>
+      <c r="F21" s="60"/>
+      <c r="G21" s="60"/>
+      <c r="H21" s="63"/>
+      <c r="I21" s="61"/>
+      <c r="J21" s="4"/>
       <c r="K21" s="5"/>
       <c r="L21" s="5"/>
       <c r="M21" s="6"/>
-      <c r="N21" s="55"/>
+      <c r="N21" s="64"/>
     </row>
     <row r="22" ht="15.5" customHeight="1" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
-      <c r="B22" s="57"/>
-      <c r="C22" s="53"/>
-      <c r="D22" s="53"/>
-      <c r="E22" s="53"/>
-      <c r="F22" s="52"/>
-      <c r="G22" s="52"/>
-      <c r="H22" s="52" t="s">
+      <c r="B22" s="66"/>
+      <c r="C22" s="61"/>
+      <c r="D22" s="61"/>
+      <c r="E22" s="61"/>
+      <c r="F22" s="60"/>
+      <c r="G22" s="60"/>
+      <c r="H22" s="60" t="s">
         <v>34</v>
       </c>
-      <c r="I22" s="53"/>
+      <c r="I22" s="61"/>
+      <c r="J22" s="4"/>
       <c r="K22" s="5"/>
       <c r="L22" s="5"/>
       <c r="M22" s="6"/>
-      <c r="N22" s="55"/>
+      <c r="N22" s="64"/>
     </row>
     <row r="23" ht="15.5" customHeight="1" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
-      <c r="B23" s="57"/>
+      <c r="B23" s="66"/>
       <c r="C23" s="3"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
@@ -1543,14 +1644,15 @@
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
+      <c r="J23" s="4"/>
       <c r="K23" s="5"/>
       <c r="L23" s="5"/>
       <c r="M23" s="6"/>
-      <c r="N23" s="55"/>
+      <c r="N23" s="64"/>
     </row>
     <row r="24" ht="15.5" customHeight="1" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
-      <c r="B24" s="57"/>
+      <c r="B24" s="66"/>
       <c r="C24" s="3"/>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
@@ -1558,14 +1660,15 @@
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
+      <c r="J24" s="4"/>
       <c r="K24" s="5"/>
       <c r="L24" s="5"/>
       <c r="M24" s="6"/>
-      <c r="N24" s="55"/>
+      <c r="N24" s="64"/>
     </row>
     <row r="25" ht="15.5" customHeight="1" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5"/>
-      <c r="B25" s="57"/>
+      <c r="B25" s="66"/>
       <c r="C25" s="3"/>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
@@ -1573,14 +1676,15 @@
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
+      <c r="J25" s="4"/>
       <c r="K25" s="5"/>
       <c r="L25" s="5"/>
       <c r="M25" s="6"/>
-      <c r="N25" s="55"/>
+      <c r="N25" s="64"/>
     </row>
     <row r="26" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5"/>
-      <c r="B26" s="56"/>
+      <c r="B26" s="65"/>
       <c r="C26" s="3"/>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
@@ -1588,14 +1692,15 @@
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
+      <c r="J26" s="4"/>
       <c r="K26" s="5"/>
       <c r="L26" s="5"/>
       <c r="M26" s="6"/>
-      <c r="N26" s="55"/>
+      <c r="N26" s="64"/>
     </row>
     <row r="27" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5"/>
-      <c r="B27" s="56"/>
+      <c r="B27" s="65"/>
       <c r="C27" s="3"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
@@ -1603,28 +1708,31 @@
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
+      <c r="J27" s="4"/>
       <c r="K27" s="5"/>
       <c r="L27" s="5"/>
       <c r="M27" s="6"/>
-      <c r="N27" s="55"/>
+      <c r="N27" s="64"/>
     </row>
     <row r="28" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5"/>
-      <c r="B28" s="56"/>
+      <c r="B28" s="65"/>
       <c r="C28" s="3"/>
       <c r="D28" s="1"/>
+      <c r="E28" s="62"/>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
+      <c r="J28" s="4"/>
       <c r="K28" s="5"/>
       <c r="L28" s="5"/>
       <c r="M28" s="6"/>
-      <c r="N28" s="55"/>
+      <c r="N28" s="64"/>
     </row>
     <row r="29" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5"/>
-      <c r="B29" s="56"/>
+      <c r="B29" s="65"/>
       <c r="C29" s="3"/>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
@@ -1632,13 +1740,15 @@
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
+      <c r="J29" s="4"/>
       <c r="K29" s="5"/>
       <c r="L29" s="5"/>
       <c r="M29" s="6"/>
-      <c r="N29" s="55"/>
-    </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B30" s="56"/>
+      <c r="N29" s="64"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="1"/>
+      <c r="B30" s="65"/>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
     </row>

--- a/templates/CLF_CoNgay.xlsx
+++ b/templates/CLF_CoNgay.xlsx
@@ -720,6 +720,9 @@
     <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -758,9 +761,6 @@
     </xf>
     <xf numFmtId="165" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1198,9 +1198,9 @@
     <col min="24" max="251" width="8.81640625" style="5" customWidth="1"/>
     <col min="252" max="252" width="2.36328125" style="5" customWidth="1"/>
     <col min="253" max="253" width="8" style="5" customWidth="1"/>
-    <col min="254" max="254" style="5" hidden="1" customWidth="1"/>
+    <col min="254" max="254" width="9" style="5" hidden="1" customWidth="1"/>
     <col min="255" max="255" width="55" style="5" customWidth="1"/>
-    <col min="256" max="16385" style="5" hidden="1" customWidth="1"/>
+    <col min="256" max="16385" width="9" style="5" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="77" customHeight="1" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -1480,36 +1480,36 @@
     </row>
     <row r="13" ht="21" customHeight="1" spans="1:13" s="45" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="46"/>
-      <c r="B13" s="47" t="s">
-        <v>27</v>
-      </c>
+      <c r="B13" s="47"/>
       <c r="C13" s="47"/>
       <c r="D13" s="47"/>
       <c r="E13" s="47"/>
       <c r="F13" s="47"/>
-      <c r="G13" s="47"/>
-      <c r="H13" s="47"/>
-      <c r="I13" s="48">
+      <c r="G13" s="47" t="s">
+        <v>27</v>
+      </c>
+      <c r="H13" s="48"/>
+      <c r="I13" s="49">
         <f>SUM(I6:I12)</f>
         <v>74990000</v>
       </c>
-      <c r="J13" s="49"/>
-      <c r="K13" s="50"/>
-      <c r="L13" s="50"/>
-      <c r="M13" s="51"/>
+      <c r="J13" s="50"/>
+      <c r="K13" s="51"/>
+      <c r="L13" s="51"/>
+      <c r="M13" s="52"/>
     </row>
     <row r="14" ht="21" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
-      <c r="B14" s="47" t="s">
-        <v>28</v>
-      </c>
+      <c r="B14" s="47"/>
       <c r="C14" s="47"/>
       <c r="D14" s="47"/>
       <c r="E14" s="47"/>
       <c r="F14" s="47"/>
-      <c r="G14" s="47"/>
-      <c r="H14" s="47"/>
-      <c r="I14" s="52">
+      <c r="G14" s="47" t="s">
+        <v>28</v>
+      </c>
+      <c r="H14" s="48"/>
+      <c r="I14" s="53">
         <f>I13*8%</f>
         <v>5999200</v>
       </c>
@@ -1517,53 +1517,53 @@
     </row>
     <row r="15" ht="21" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
-      <c r="B15" s="47" t="s">
-        <v>29</v>
-      </c>
+      <c r="B15" s="47"/>
       <c r="C15" s="47"/>
       <c r="D15" s="47"/>
       <c r="E15" s="47"/>
       <c r="F15" s="47"/>
-      <c r="G15" s="47"/>
-      <c r="H15" s="47"/>
-      <c r="I15" s="52">
+      <c r="G15" s="47" t="s">
+        <v>29</v>
+      </c>
+      <c r="H15" s="48"/>
+      <c r="I15" s="53">
         <f>I13+I14</f>
         <v>80989200</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
-      <c r="B16" s="53"/>
-      <c r="C16" s="54"/>
+      <c r="B16" s="54"/>
+      <c r="C16" s="55"/>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
     </row>
     <row r="17" ht="61" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="2"/>
-      <c r="C17" s="55" t="s">
+      <c r="C17" s="56" t="s">
         <v>30</v>
       </c>
-      <c r="D17" s="55"/>
-      <c r="E17" s="56"/>
-      <c r="F17" s="57"/>
-      <c r="G17" s="57"/>
-      <c r="H17" s="58" t="s">
+      <c r="D17" s="56"/>
+      <c r="E17" s="57"/>
+      <c r="F17" s="58"/>
+      <c r="G17" s="58"/>
+      <c r="H17" s="59" t="s">
         <v>31</v>
       </c>
-      <c r="I17" s="59"/>
+      <c r="I17" s="60"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="2"/>
-      <c r="C18" s="60" t="s">
+      <c r="C18" s="47" t="s">
         <v>32</v>
       </c>
-      <c r="D18" s="60"/>
+      <c r="D18" s="47"/>
       <c r="E18" s="61"/>
-      <c r="F18" s="60"/>
-      <c r="G18" s="60"/>
-      <c r="H18" s="60" t="s">
+      <c r="F18" s="47"/>
+      <c r="G18" s="47"/>
+      <c r="H18" s="47" t="s">
         <v>33</v>
       </c>
       <c r="I18" s="61"/>
@@ -1573,9 +1573,9 @@
       <c r="B19" s="62"/>
       <c r="C19" s="61"/>
       <c r="D19" s="61"/>
-      <c r="E19" s="60"/>
-      <c r="F19" s="60"/>
-      <c r="G19" s="60"/>
+      <c r="E19" s="47"/>
+      <c r="F19" s="47"/>
+      <c r="G19" s="47"/>
       <c r="H19" s="63"/>
       <c r="I19" s="61"/>
       <c r="J19" s="4"/>
@@ -1586,12 +1586,12 @@
     </row>
     <row r="20" ht="24" customHeight="1" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5"/>
-      <c r="B20" s="53"/>
+      <c r="B20" s="54"/>
       <c r="C20" s="61"/>
       <c r="D20" s="61"/>
-      <c r="E20" s="60"/>
-      <c r="F20" s="60"/>
-      <c r="G20" s="60"/>
+      <c r="E20" s="47"/>
+      <c r="F20" s="47"/>
+      <c r="G20" s="47"/>
       <c r="H20" s="63"/>
       <c r="I20" s="61"/>
       <c r="J20" s="4"/>
@@ -1605,9 +1605,9 @@
       <c r="B21" s="65"/>
       <c r="C21" s="61"/>
       <c r="D21" s="61"/>
-      <c r="E21" s="60"/>
-      <c r="F21" s="60"/>
-      <c r="G21" s="60"/>
+      <c r="E21" s="47"/>
+      <c r="F21" s="47"/>
+      <c r="G21" s="47"/>
       <c r="H21" s="63"/>
       <c r="I21" s="61"/>
       <c r="J21" s="4"/>
@@ -1622,9 +1622,9 @@
       <c r="C22" s="61"/>
       <c r="D22" s="61"/>
       <c r="E22" s="61"/>
-      <c r="F22" s="60"/>
-      <c r="G22" s="60"/>
-      <c r="H22" s="60" t="s">
+      <c r="F22" s="47"/>
+      <c r="G22" s="47"/>
+      <c r="H22" s="47" t="s">
         <v>34</v>
       </c>
       <c r="I22" s="61"/>
@@ -1762,13 +1762,13 @@
     <mergeCell ref="C7:C9"/>
     <mergeCell ref="B10:B12"/>
     <mergeCell ref="C10:C12"/>
-    <mergeCell ref="B13:H13"/>
-    <mergeCell ref="B14:H14"/>
-    <mergeCell ref="B15:H15"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="G15:H15"/>
     <mergeCell ref="C17:D17"/>
   </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" scale="55" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" scale="55" fitToWidth="1" fitToHeight="0" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/templates/CLF_CoNgay.xlsx
+++ b/templates/CLF_CoNgay.xlsx
@@ -1485,7 +1485,7 @@
       <c r="D13" s="47"/>
       <c r="E13" s="47"/>
       <c r="F13" s="47"/>
-      <c r="G13" s="47" t="s">
+      <c r="G13" s="48" t="s">
         <v>27</v>
       </c>
       <c r="H13" s="48"/>
@@ -1505,7 +1505,7 @@
       <c r="D14" s="47"/>
       <c r="E14" s="47"/>
       <c r="F14" s="47"/>
-      <c r="G14" s="47" t="s">
+      <c r="G14" s="48" t="s">
         <v>28</v>
       </c>
       <c r="H14" s="48"/>
@@ -1522,7 +1522,7 @@
       <c r="D15" s="47"/>
       <c r="E15" s="47"/>
       <c r="F15" s="47"/>
-      <c r="G15" s="47" t="s">
+      <c r="G15" s="48" t="s">
         <v>29</v>
       </c>
       <c r="H15" s="48"/>

--- a/templates/CLF_CoNgay.xlsx
+++ b/templates/CLF_CoNgay.xlsx
@@ -341,7 +341,7 @@
     </font>
     <font>
       <b/>
-      <color theme="1"/>
+      <color rgb="FF243139"/>
       <family val="1"/>
       <sz val="18"/>
       <name val="Times New Roman"/>
@@ -459,7 +459,7 @@
       <name val="Times New Roman"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -468,14 +468,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.3999755851924192"/>
+        <fgColor rgb="FF9CCDC9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DCCC9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.3999755851924192"/>
-        <bgColor rgb="FF000000"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -648,22 +654,22 @@
     <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -726,7 +732,7 @@
     <xf numFmtId="0" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="14" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="14" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
